--- a/test_data/birds/data/additional-ro-crate-metadata.xlsx
+++ b/test_data/birds/data/additional-ro-crate-metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bbb/sandbox/casey-ro-crate-html-lite/ro-crate-html-lite/test_data/birds/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bbb/sandbox/ro-crate-static-site/test_data/birds/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B498A2E-3344-E446-B2E4-D77B3973741C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314C9C66-4A59-0A45-BE2A-32C01278ED0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="32440" windowHeight="18160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RootDataset" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="77">
   <si>
     <t>name</t>
   </si>
@@ -104,9 +104,6 @@
     <t>custom:scientificName</t>
   </si>
   <si>
-    <t>isRef_custom:image</t>
-  </si>
-  <si>
     <t>isRef_custom:callAudio</t>
   </si>
   <si>
@@ -161,15 +158,6 @@
     <t>the translation of this entry's story</t>
   </si>
   <si>
-    <t>arcp://name,custom/terms#image</t>
-  </si>
-  <si>
-    <t>image</t>
-  </si>
-  <si>
-    <t>the bird image</t>
-  </si>
-  <si>
     <t>callAudio</t>
   </si>
   <si>
@@ -279,6 +267,9 @@
   </si>
   <si>
     <t>about them</t>
+  </si>
+  <si>
+    <t>isRef_image</t>
   </si>
 </sst>
 </file>
@@ -707,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -715,7 +706,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -797,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>6</v>
@@ -824,22 +815,22 @@
         <v>19</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -848,10 +839,10 @@
         <v>#magpie</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E2" s="5" t="str">
         <f>K2</f>
@@ -861,40 +852,40 @@
         <v>3</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -920,52 +911,52 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1280,10 +1271,10 @@
         <v>#person_1</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1319,128 +1310,114 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>35</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1465,21 +1442,21 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>

--- a/test_data/birds/data/additional-ro-crate-metadata.xlsx
+++ b/test_data/birds/data/additional-ro-crate-metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bbb/sandbox/ro-crate-static-site/test_data/birds/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314C9C66-4A59-0A45-BE2A-32C01278ED0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F46D9A-6DB8-3444-BCA1-848F31DA0FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1140" windowWidth="30240" windowHeight="18160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RootDataset" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="CustomFields" sheetId="6" r:id="rId6"/>
     <sheet name="AboutPage" sheetId="7" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="85">
   <si>
     <t>name</t>
   </si>
@@ -56,9 +59,6 @@
     <t>@type</t>
   </si>
   <si>
-    <t>[Dataset,RepositoryCollection]</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
@@ -83,9 +83,6 @@
     <t>isRef_pcdm:memberOf</t>
   </si>
   <si>
-    <t>isRef_speaker</t>
-  </si>
-  <si>
     <t>datePublished</t>
   </si>
   <si>
@@ -227,9 +224,6 @@
     <t>Birds</t>
   </si>
   <si>
-    <t>bird stories</t>
-  </si>
-  <si>
     <t>birdy</t>
   </si>
   <si>
@@ -270,13 +264,46 @@
   </si>
   <si>
     <t>isRef_image</t>
+  </si>
+  <si>
+    <t>isRef_ldac:speaker</t>
+  </si>
+  <si>
+    <t>Person</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>[Dataset, RepositoryCollection]</t>
+  </si>
+  <si>
+    <t>inLanguage</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>ldac:subjectLanguage</t>
+  </si>
+  <si>
+    <t>ldac:metadataIsPublic</t>
+  </si>
+  <si>
+    <t>This is an example bird collection</t>
+  </si>
+  <si>
+    <t>2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,8 +317,33 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,6 +359,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EAFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -338,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -361,6 +431,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,6 +459,67 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="RootDataset"/>
+      <sheetName val="@context"/>
+      <sheetName val="Custom Terms"/>
+      <sheetName val="Authors"/>
+      <sheetName val="Publishers"/>
+      <sheetName val="Licenses"/>
+      <sheetName val="Provenance"/>
+      <sheetName val="People"/>
+      <sheetName val="Places"/>
+      <sheetName val="Localities"/>
+      <sheetName val="Objects"/>
+      <sheetName val="Files"/>
+      <sheetName val="Schemas"/>
+      <sheetName val="Columns"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>#LDaCA</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>https://ror.org/00rqy9422</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>https://creativecommons.org/licenses/by/4.0/</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -663,60 +807,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="15" style="9" customWidth="1"/>
+    <col min="2" max="2" width="29.5" style="9" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B4" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="15" t="str">
+        <f>[1]Authors!A2</f>
+        <v>#LDaCA</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="15" t="str">
+        <f>[1]Publishers!A2</f>
+        <v>https://ror.org/00rqy9422</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="15" t="str">
+        <f>[1]Licenses!A2</f>
+        <v>https://creativecommons.org/licenses/by/4.0/</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="16" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -739,18 +934,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -788,49 +983,49 @@
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -839,10 +1034,10 @@
         <v>#magpie</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5" t="str">
         <f>K2</f>
@@ -852,40 +1047,40 @@
         <v>3</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="P2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -911,52 +1106,52 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1246,35 +1441,41 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.5" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="1" max="2" width="26.5" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="str">
-        <f>LOWER(_xlfn.CONCAT("#", SUBSTITUTE(B2, " ", "_")))</f>
+        <f>LOWER(_xlfn.CONCAT("#", SUBSTITUTE(C2, " ", "_")))</f>
         <v>#person_1</v>
       </c>
-      <c r="B2" t="s">
-        <v>65</v>
+      <c r="B2" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1305,119 +1506,119 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
         <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
         <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
         <v>44</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
         <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
         <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1431,6 +1632,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1442,21 +1644,21 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
         <v>52</v>
-      </c>
-      <c r="B2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
